--- a/education_surveys/045_linear_algebra_concepts_survey--education_surveys.xlsx
+++ b/education_surveys/045_linear_algebra_concepts_survey--education_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -773,12 +773,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>linear_algebra_concepts_rating_justification</t>
+          <t>linear_algebra_concepts_rating_justification_2</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>Linear Algebra Concepts Rating Justification</t>
+          <t>Linear Algebra Concepts Rating Justification 2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr"/>
@@ -801,7 +801,7 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>Linear Algebra Concept Scale</t>
+          <t>Linear Algebra Concept Rating Scale</t>
         </is>
       </c>
       <c r="D16" t="inlineStr"/>
@@ -824,7 +824,7 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>Linear Algebra Concept Scale Value</t>
+          <t>Linear Algebra Concept Rating Scale Value</t>
         </is>
       </c>
       <c r="D17" t="inlineStr"/>
@@ -847,7 +847,7 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>Linear Algebra Concept Scale Justification</t>
+          <t>Linear Algebra Concept Rating Scale Justification</t>
         </is>
       </c>
       <c r="D18" t="inlineStr"/>
@@ -865,12 +865,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>linear_algebra_concept_rating_scale_justification</t>
+          <t>linear_algebra_concept_rating_scale_justification_2</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>Linear Algebra Concept Scale Justification</t>
+          <t>Linear Algebra Concept Rating Scale Justification 2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr"/>
@@ -934,12 +934,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>linear_algebra_concept_scale_value_justification</t>
+          <t>linear_algebra_concept_scale_value_justification_2</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>Linear Algebra Concept Scale Value Justification</t>
+          <t>Linear Algebra Concept Scale Value Justification 2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr"/>
@@ -957,12 +957,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>linear_algebra_concept_scale_justification</t>
+          <t>linear_algebra_concept_scale_justification_2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>Linear Algebra Concept Scale Justification</t>
+          <t>Linear Algebra Concept Scale Justification 2</t>
         </is>
       </c>
       <c r="D23" t="inlineStr"/>
@@ -980,7 +980,7 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>linear_algebra_concept_scale</t>
+          <t>linear_algebra_concept_scale_2</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
@@ -1026,12 +1026,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>linear_algebra_concepts_rating_justification</t>
+          <t>linear_algebra_concepts_rating_justification_3</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>Linear Algebra Concepts Rating Justification</t>
+          <t>Linear Algebra Concepts Rating Justification 3</t>
         </is>
       </c>
       <c r="D26" t="inlineStr"/>
@@ -1049,12 +1049,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>linear_algebra_concept_scale_value_justification</t>
+          <t>linear_algebra_concept_scale_value_justification_3</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>Linear Algebra Concept Scale Value Justification</t>
+          <t>Linear Algebra Concept Scale Value Justification 3</t>
         </is>
       </c>
       <c r="D27" t="inlineStr"/>
@@ -1072,12 +1072,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>linear_algebra_important_concepts_scale</t>
+          <t>linear_algebra_important_concepts_scale_2</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>Linear Algebra Important Concepts Scale</t>
+          <t>Linear Algebra Important Concepts Scale 2</t>
         </is>
       </c>
       <c r="D28" t="inlineStr"/>
@@ -1330,7 +1330,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>linear_algebra_concept_scale_choices</t>
+          <t>linear_algebra_concept_scale_2_choices</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -1347,7 +1347,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>linear_algebra_concept_scale_choices</t>
+          <t>linear_algebra_concept_scale_2_choices</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -1364,7 +1364,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>linear_algebra_important_concepts_scale_choices</t>
+          <t>linear_algebra_important_concepts_scale_2_choices</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -1381,7 +1381,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>linear_algebra_important_concepts_scale_choices</t>
+          <t>linear_algebra_important_concepts_scale_2_choices</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
